--- a/docs/files/exports/readme1.xlsx
+++ b/docs/files/exports/readme1.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2,541 words</t>
+          <t>2,705 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>🔍 Complete SEO Framework &amp;amp; Tech Stack Guide (2026) A comprehensive reference for developers and teams choosing the right technology stack for SEO-optimized websites. 📋 Table of Contents SEO Scoring Criteria Frontend ...</t>
+          <t>🔍 Complete SEO Framework &amp;amp; Tech Stack Guide (2026) A comprehensive reference for developers and teams choosing the right technology stack for SEO-optimized websites. 📋 Table of Contents + Add to Scope SEO Scoring Cri...</t>
         </is>
       </c>
     </row>
